--- a/data/downloads/BNDES_2452.xlsx
+++ b/data/downloads/BNDES_2452.xlsx
@@ -30,6 +30,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="13"/>
     </font>
     <font>
@@ -39,6 +40,7 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00000000"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -55,9 +57,7 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
-      </patternFill>
+      <patternFill patternType="solid"/>
     </fill>
   </fills>
   <borders count="2">
